--- a/C++kadai/kadai05.xlsx
+++ b/C++kadai/kadai05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\OracleLinux_8_5\home\integral\c++\repo\C++kadai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4043FE3-D58A-468D-BD5C-FD54C11DB341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE39A0D-3BA2-4D28-9253-8DA85535A527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7914A6A9-3BE6-446B-95D5-AC1EDD28F45B}"/>
   </bookViews>
@@ -25,29 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>・初期状態は待機中であること</t>
-  </si>
-  <si>
-    <t>・着信中または発信中に、受話(自分または相手)があれば、通話中に遷移する</t>
-  </si>
-  <si>
-    <t>・電源OFF以外の状態のときに、電源OFFを選択すると、電源OFFになる。</t>
-  </si>
-  <si>
-    <t>・着信中の発信は受け付けない。</t>
-  </si>
-  <si>
-    <t>・発信中の着信は受け付けない。</t>
-  </si>
-  <si>
-    <t>・待機中の場合のみ、着信、発信を受け付ける。</t>
-  </si>
-  <si>
-    <t>・着信中、発信中に通話終了すると待機中に戻る。</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -117,15 +95,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>235858</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>105833</xdr:colOff>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>235857</xdr:rowOff>
+      <xdr:rowOff>200024</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -140,8 +118,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9736667" y="2426608"/>
-          <a:ext cx="1375833" cy="730249"/>
+          <a:off x="9601200" y="2343150"/>
+          <a:ext cx="1371599" cy="714374"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -202,16 +180,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>105833</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>653142</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>235857</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
+      <xdr:rowOff>226332</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>235857</xdr:rowOff>
+      <xdr:rowOff>226332</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -226,8 +204,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4233333" y="2426607"/>
-          <a:ext cx="1375834" cy="730250"/>
+          <a:off x="4082142" y="2369457"/>
+          <a:ext cx="1371601" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -275,16 +253,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>105832</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>653141</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>235857</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>105833</xdr:colOff>
+      <xdr:rowOff>226332</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>653142</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>235857</xdr:rowOff>
+      <xdr:rowOff>226332</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -299,8 +277,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6984999" y="3156857"/>
-          <a:ext cx="1375834" cy="730250"/>
+          <a:off x="6825341" y="3083832"/>
+          <a:ext cx="1371601" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -348,16 +326,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>105832</xdr:colOff>
+      <xdr:rowOff>211515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>653141</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>211515</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -372,8 +350,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1481667" y="2411790"/>
-          <a:ext cx="1375832" cy="730250"/>
+          <a:off x="1338943" y="2354640"/>
+          <a:ext cx="1371598" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -421,16 +399,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>105833</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>653142</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
+      <xdr:rowOff>211515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>211515</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -445,8 +423,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4233333" y="3872290"/>
-          <a:ext cx="1375834" cy="730250"/>
+          <a:off x="4082142" y="3783390"/>
+          <a:ext cx="1371601" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -495,15 +473,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>612775</xdr:colOff>
+      <xdr:colOff>474284</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>78846</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>115359</xdr:colOff>
+      <xdr:rowOff>69321</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>662668</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>83608</xdr:rowOff>
+      <xdr:rowOff>74083</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -518,8 +496,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="612775" y="2756429"/>
-          <a:ext cx="878417" cy="4762"/>
+          <a:off x="474284" y="2688696"/>
+          <a:ext cx="874184" cy="4762"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -551,16 +529,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>101750</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>649059</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>224291</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>101751</xdr:colOff>
+      <xdr:rowOff>214766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>649060</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>224291</xdr:rowOff>
+      <xdr:rowOff>214766</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -575,8 +553,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2853417" y="2901874"/>
-          <a:ext cx="1375834" cy="0"/>
+          <a:off x="2706459" y="2834141"/>
+          <a:ext cx="1371601" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -608,16 +586,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>111503</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>101750</xdr:colOff>
+      <xdr:rowOff>101978</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>649059</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>216278</xdr:rowOff>
+      <xdr:rowOff>206753</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -634,8 +612,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5609167" y="2789086"/>
-          <a:ext cx="1371750" cy="591609"/>
+          <a:off x="5453743" y="2721353"/>
+          <a:ext cx="1367516" cy="581025"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -667,16 +645,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>224291</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>105832</xdr:colOff>
+      <xdr:rowOff>214766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>653141</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>101978</xdr:rowOff>
+      <xdr:rowOff>92453</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -693,8 +671,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="5609167" y="3632124"/>
-          <a:ext cx="1375832" cy="607937"/>
+          <a:off x="5453743" y="3548516"/>
+          <a:ext cx="1371598" cy="592062"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -726,16 +704,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>101750</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>649059</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>240619</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>101751</xdr:colOff>
+      <xdr:rowOff>231094</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>649060</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>240619</xdr:rowOff>
+      <xdr:rowOff>231094</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -750,8 +728,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2853417" y="2674786"/>
-          <a:ext cx="1375834" cy="0"/>
+          <a:off x="2706459" y="2612344"/>
+          <a:ext cx="1371601" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -783,447 +761,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>467783</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>235856</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>97830</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1965</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="75" name="グループ化 74">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62039728-08C5-3D94-F28D-353250228A32}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm flipH="1">
-          <a:off x="8011583" y="473981"/>
-          <a:ext cx="2373247" cy="2623609"/>
-          <a:chOff x="1733550" y="476250"/>
-          <a:chExt cx="8210550" cy="2628900"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="67" name="直線コネクタ 66">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C55B8DA7-13A9-9ED5-50A9-9F7F78B0048C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="9944100" y="485775"/>
-            <a:ext cx="0" cy="2619375"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="68" name="直線コネクタ 67">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A3A4CC2-3B32-4015-5895-2F9D5FAAA6A5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1733550" y="485775"/>
-            <a:ext cx="0" cy="1895475"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:headEnd type="triangle" w="med" len="med"/>
-            <a:tailEnd type="none" w="med" len="med"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="70" name="直線コネクタ 69">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44A48B99-FC05-160C-8BDB-A16C51098DD0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1743075" y="476250"/>
-            <a:ext cx="8191500" cy="9525"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>117040</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>306881</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>238656</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>109035</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>126910</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="76" name="グループ化 75">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2DE562F-98A4-6D6E-95D6-650216F49729}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm rot="10800000">
-          <a:off x="5603440" y="3096156"/>
-          <a:ext cx="4792595" cy="1317004"/>
-          <a:chOff x="1733550" y="446418"/>
-          <a:chExt cx="6373503" cy="1934832"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="78" name="直線コネクタ 77">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E49A37C-8C1E-122F-ED7E-39BDFD22ECE5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1733550" y="485775"/>
-            <a:ext cx="0" cy="1895475"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:headEnd type="triangle" w="med" len="med"/>
-            <a:tailEnd type="none" w="med" len="med"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="79" name="直線コネクタ 78">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{335580E1-F337-0F44-A9FA-776F4319A111}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="10800000" flipH="1">
-            <a:off x="1743073" y="446418"/>
-            <a:ext cx="6363980" cy="39360"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>6496</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>226332</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>230415</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="80" name="グループ化 79">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25F975EC-09A5-6DB9-386F-6D14BD50F911}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm flipH="1">
-          <a:off x="4807096" y="464457"/>
-          <a:ext cx="5575153" cy="1909083"/>
-          <a:chOff x="1733550" y="476250"/>
-          <a:chExt cx="8209585" cy="1912193"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="81" name="直線コネクタ 80">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F534CC8-6E07-F30A-3F2E-F4ADD969EB44}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipH="1" flipV="1">
-            <a:off x="9942379" y="489487"/>
-            <a:ext cx="756" cy="1898956"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="82" name="直線コネクタ 81">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42A6DF2E-A303-83B0-37BB-07D1A78D68D9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1733550" y="485775"/>
-            <a:ext cx="0" cy="1895475"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:headEnd type="triangle" w="med" len="med"/>
-            <a:tailEnd type="none" w="med" len="med"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="83" name="直線コネクタ 82">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94888A41-AC5B-2A7F-C3D7-EBE950392D40}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1743075" y="476250"/>
-            <a:ext cx="8191500" cy="9525"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>445372</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>216558</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>96148</xdr:colOff>
+      <xdr:rowOff>207033</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>643457</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>236416</xdr:rowOff>
+      <xdr:rowOff>226891</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -1238,7 +785,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm rot="10800000" flipH="1">
-          <a:off x="1816972" y="3074058"/>
+          <a:off x="1678481" y="3064533"/>
           <a:ext cx="2393976" cy="1210483"/>
           <a:chOff x="1733550" y="476250"/>
           <a:chExt cx="8201025" cy="1905000"/>
@@ -1334,15 +881,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>469463</xdr:colOff>
+      <xdr:colOff>330972</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>216558</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>109754</xdr:colOff>
+      <xdr:rowOff>207033</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>657063</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>236416</xdr:rowOff>
+      <xdr:rowOff>226891</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -1357,7 +904,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm rot="10800000" flipH="1">
-          <a:off x="2526863" y="3074058"/>
+          <a:off x="2388372" y="3064533"/>
           <a:ext cx="1697691" cy="972358"/>
           <a:chOff x="1733550" y="476250"/>
           <a:chExt cx="8201025" cy="1905000"/>
@@ -1453,15 +1000,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>479710</xdr:colOff>
+      <xdr:colOff>341219</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>229359</xdr:rowOff>
+      <xdr:rowOff>219833</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>467782</xdr:colOff>
+      <xdr:colOff>329291</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>228599</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -1476,8 +1023,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2537110" y="1419984"/>
-          <a:ext cx="4788672" cy="1658556"/>
+          <a:off x="2398619" y="1410458"/>
+          <a:ext cx="4788672" cy="1675641"/>
           <a:chOff x="1725529" y="485775"/>
           <a:chExt cx="8219328" cy="1898956"/>
         </a:xfrm>
@@ -1609,16 +1156,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>679412</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>233927</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3138</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>224402</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>238124</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1633,8 +1180,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2736812" y="233927"/>
-          <a:ext cx="695326" cy="228600"/>
+          <a:off x="3419474" y="485774"/>
+          <a:ext cx="2066926" cy="466725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1664,14 +1211,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>電源</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>OFF</a:t>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>ON</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1680,15 +1227,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>683533</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>241300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5142</xdr:colOff>
+      <xdr:colOff>364067</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>231774</xdr:rowOff>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88899</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1703,8 +1250,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683533" y="2432050"/>
-          <a:ext cx="697442" cy="233891"/>
+          <a:off x="364067" y="2479675"/>
+          <a:ext cx="693209" cy="228599"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1749,16 +1296,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>620486</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>230564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>73177</xdr:colOff>
+      <xdr:colOff>681718</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1964</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>134409</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1964</xdr:rowOff>
+      <xdr:rowOff>230564</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1773,8 +1320,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5576510" y="1219047"/>
-          <a:ext cx="749149" cy="243417"/>
+          <a:off x="5421086" y="1183064"/>
+          <a:ext cx="747032" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1815,15 +1362,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>420157</xdr:colOff>
+      <xdr:colOff>281666</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>211514</xdr:rowOff>
+      <xdr:rowOff>201989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>486833</xdr:colOff>
+      <xdr:colOff>348342</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>211514</xdr:rowOff>
+      <xdr:rowOff>201989</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1838,8 +1385,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3171824" y="2402264"/>
-          <a:ext cx="754592" cy="243417"/>
+          <a:off x="3024866" y="2345114"/>
+          <a:ext cx="752476" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1880,15 +1427,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>420157</xdr:colOff>
+      <xdr:colOff>281666</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>229052</xdr:rowOff>
+      <xdr:rowOff>219527</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>486833</xdr:colOff>
+      <xdr:colOff>348342</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>229053</xdr:rowOff>
+      <xdr:rowOff>219528</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1903,8 +1450,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3171824" y="2906635"/>
-          <a:ext cx="754592" cy="243418"/>
+          <a:off x="3024866" y="2838902"/>
+          <a:ext cx="752476" cy="238126"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1945,15 +1492,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>591608</xdr:colOff>
+      <xdr:colOff>453117</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>230564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>527352</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1964</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>665843</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1964</xdr:rowOff>
+      <xdr:rowOff>230564</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1968,8 +1515,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1279525" y="3896631"/>
-          <a:ext cx="762151" cy="243416"/>
+          <a:off x="1138917" y="3802439"/>
+          <a:ext cx="760035" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2010,15 +1557,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>410633</xdr:colOff>
+      <xdr:colOff>272142</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>40064</xdr:rowOff>
+      <xdr:rowOff>30539</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>477307</xdr:colOff>
+      <xdr:colOff>338816</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>40064</xdr:rowOff>
+      <xdr:rowOff>30539</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2033,8 +1580,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2474383" y="3691314"/>
-          <a:ext cx="754591" cy="243417"/>
+          <a:off x="2329542" y="3602414"/>
+          <a:ext cx="752474" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2075,15 +1622,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>138491</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>74083</xdr:rowOff>
+      <xdr:rowOff>64558</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
+      <xdr:colOff>464759</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>55033</xdr:rowOff>
+      <xdr:rowOff>45508</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2098,8 +1645,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="138491" y="2508250"/>
-          <a:ext cx="464759" cy="467783"/>
+          <a:off x="0" y="2445808"/>
+          <a:ext cx="464759" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartConnector">
           <a:avLst/>
@@ -2142,16 +1689,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>602156</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>85449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>16747</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>104499</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>477149</xdr:colOff>
+      <xdr:colOff>376758</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>85449</xdr:rowOff>
+      <xdr:rowOff>66399</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2166,7 +1713,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11675347" y="2485749"/>
+          <a:off x="11574956" y="2466699"/>
           <a:ext cx="460402" cy="457200"/>
           <a:chOff x="14446623" y="2461932"/>
           <a:chExt cx="454959" cy="451597"/>
@@ -2284,15 +1831,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>50206</xdr:colOff>
+      <xdr:colOff>149840</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>32221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213313</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>51271</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>113679</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>51270</xdr:rowOff>
+      <xdr:rowOff>32220</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2307,8 +1854,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5553539" y="2972271"/>
-          <a:ext cx="751390" cy="243416"/>
+          <a:off x="5636240" y="2651596"/>
+          <a:ext cx="749273" cy="238124"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2339,7 +1886,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>応答有</a:t>
+            <a:t>受話</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2349,15 +1896,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>189318</xdr:colOff>
+      <xdr:colOff>155602</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>30538</xdr:rowOff>
+      <xdr:rowOff>40063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>255993</xdr:colOff>
+      <xdr:colOff>222277</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>30539</xdr:rowOff>
+      <xdr:rowOff>40064</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2372,8 +1919,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5692651" y="3681788"/>
-          <a:ext cx="754592" cy="243418"/>
+          <a:off x="5642002" y="3611938"/>
+          <a:ext cx="752475" cy="238126"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2404,7 +1951,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>応答有</a:t>
+            <a:t>受話</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2413,180 +1960,340 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>457134</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>216557</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>97829</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>216557</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="127" name="グループ化 126">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35F0BF4E-A24F-950E-1CEE-DBE7D780598E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm flipH="1">
-          <a:off x="1828734" y="454682"/>
-          <a:ext cx="8556095" cy="1905000"/>
-          <a:chOff x="1733550" y="476250"/>
-          <a:chExt cx="8211307" cy="1908481"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="128" name="直線コネクタ 127">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B27CF6-6869-4E01-61CF-ED4E9FDFFD2E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipH="1" flipV="1">
-            <a:off x="9944100" y="485775"/>
-            <a:ext cx="757" cy="1898956"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="129" name="直線コネクタ 128">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E92E66-40D7-9659-E46A-9BE7266DFFA4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1733550" y="485775"/>
-            <a:ext cx="0" cy="1895475"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:headEnd type="triangle" w="med" len="med"/>
-            <a:tailEnd type="none" w="med" len="med"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="130" name="直線コネクタ 129">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E22AA83-93EA-498B-DF63-FDCCF0E45B47}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1743075" y="476250"/>
-            <a:ext cx="8191500" cy="9525"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>668368</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>216807</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>677891</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>199189</xdr:rowOff>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>75924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>602156</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="134" name="直線矢印コネクタ 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{682B18F4-8999-CAFB-741E-2092C4FA51E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="119" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="10972799" y="2695299"/>
+          <a:ext cx="602157" cy="5038"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>91888</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>131109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>546847</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="131" name="テキスト ボックス 130">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8402B84-2240-4664-4865-9667A01E5143}"/>
+        <xdr:cNvPr id="135" name="フローチャート: 結合子 134">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88EC9A07-24EB-6398-9661-656BDEAA7A72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25383564" y="2484344"/>
+          <a:ext cx="454959" cy="451597"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>128307</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>167546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>515470</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>83456</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="136" name="フローチャート: 結合子 135">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FA2959C-030E-F892-8F5C-181B126B534E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25419983" y="2520781"/>
+          <a:ext cx="387163" cy="386557"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形: 角を丸くする 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2657B26D-1C0E-8FB8-73A8-8D45F9F5399A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="952500" y="381000"/>
+          <a:ext cx="7953375" cy="4619625"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E714929-605A-002B-826E-8029D291BD7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="4" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8905875" y="2690813"/>
+          <a:ext cx="695325" cy="9524"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>659342</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>231775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>222249</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{343FE4E4-E9DD-0326-0E6A-8690FC0C2CA1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2594,8 +2301,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6154768" y="216807"/>
-          <a:ext cx="695323" cy="220507"/>
+          <a:off x="8888942" y="2374900"/>
+          <a:ext cx="693209" cy="228599"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2632,339 +2339,6 @@
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
             <a:t>OFF</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>668366</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>226083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>677893</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>216558</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="132" name="テキスト ボックス 131">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2816A378-8C89-92ED-E9C1-4060A7D04CFC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8897966" y="226083"/>
-          <a:ext cx="695327" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>電源</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>OFF</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>60446</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>32221</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>69973</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>27988</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="133" name="テキスト ボックス 132">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4585E49E-B24D-3209-D848-819E093CD506}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9661646" y="4080346"/>
-          <a:ext cx="695327" cy="233892"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>電源</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>OFF</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>101750</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>112183</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>1059</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>114865</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="134" name="直線矢印コネクタ 133">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{682B18F4-8999-CAFB-741E-2092C4FA51E8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11108417" y="2789766"/>
-          <a:ext cx="587225" cy="2682"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="arrow" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>91888</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>131109</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>546847</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>112059</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="135" name="フローチャート: 結合子 134">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88EC9A07-24EB-6398-9661-656BDEAA7A72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="25383564" y="2484344"/>
-          <a:ext cx="454959" cy="451597"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartConnector">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>128307</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>167546</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>515470</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>83456</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="136" name="フローチャート: 結合子 135">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FA2959C-030E-F892-8F5C-181B126B534E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="25419983" y="2520781"/>
-          <a:ext cx="387163" cy="386557"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartConnector">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -3271,45 +2645,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDAADF2A-B5EF-4633-A97C-D64FF936C519}">
-  <dimension ref="A22:A28"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/C++kadai/kadai05.xlsx
+++ b/C++kadai/kadai05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\OracleLinux_8_5\home\integral\c++\repo\C++kadai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE39A0D-3BA2-4D28-9253-8DA85535A527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABE4313-8BF9-408A-96A8-68316671E081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7914A6A9-3BE6-446B-95D5-AC1EDD28F45B}"/>
   </bookViews>
